--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MINNESOTA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MINNESOTA_2015.xlsx
@@ -409,7 +409,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="4">
@@ -1327,7 +1327,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="55">
@@ -1813,7 +1813,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="82">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C83">
@@ -2605,7 +2605,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="126">
@@ -3973,7 +3973,7 @@
         <v>74</v>
       </c>
       <c r="D201">
-        <v>0.009561958909419821</v>
+        <v>0.00956195890941982</v>
       </c>
     </row>
     <row r="202">
@@ -4261,7 +4261,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="218">
@@ -4351,7 +4351,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="223">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C224">
@@ -4981,7 +4981,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="258">
@@ -5431,7 +5431,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="283">
@@ -5593,7 +5593,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="292">
@@ -5701,7 +5701,7 @@
         <v>7</v>
       </c>
       <c r="D297">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="298">
@@ -6079,7 +6079,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="319">
@@ -6331,7 +6331,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="333">
@@ -7375,7 +7375,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="391">
@@ -7483,7 +7483,7 @@
         <v>71</v>
       </c>
       <c r="D396">
-        <v>0.009174311926605505</v>
+        <v>0.009174311926605503</v>
       </c>
     </row>
     <row r="397">
@@ -8527,7 +8527,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="455">
@@ -9715,7 +9715,7 @@
         <v>71</v>
       </c>
       <c r="D520">
-        <v>0.009174311926605505</v>
+        <v>0.009174311926605503</v>
       </c>
     </row>
     <row r="521">
@@ -9949,7 +9949,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="534">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C624">
@@ -15277,7 +15277,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="830">
@@ -16087,7 +16087,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="875">
@@ -16141,7 +16141,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="878">
@@ -17527,7 +17527,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="955">
@@ -18157,7 +18157,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="990">
@@ -18463,7 +18463,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="1007">
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="1022">
@@ -19399,7 +19399,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="1059">
@@ -19651,7 +19651,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>0.0009045096265667399</v>
+        <v>0.00090450962656674</v>
       </c>
     </row>
     <row r="1073">
